--- a/Documents/USLS_Documents/AC-STUDENT-MONITORING-_Template_.xlsx
+++ b/Documents/USLS_Documents/AC-STUDENT-MONITORING-_Template_.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10323"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddie/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github_Projects\CAPSTONE-USLS-MVP\Documents\USLS_Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC4D0D4-DC2C-D640-995C-6AEA563AF5EE}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1520A4-2A32-4317-A16E-DEF6AA411E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="480" windowWidth="28800" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CUR 2021-2022&lt;Template&gt;" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KRwrGkAilA19PJFCr41ynJFfxNbFYjGE5sugTfn+iD0="/>
     </ext>
@@ -82,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="114">
   <si>
     <t>PROGRAM: MBA</t>
   </si>
@@ -421,6 +432,9 @@
   </si>
   <si>
     <t>IRA</t>
+  </si>
+  <si>
+    <t>AAA</t>
   </si>
 </sst>
 </file>
@@ -851,12 +865,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="101">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -938,12 +952,6 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -971,16 +979,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1355,32 +1354,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN1000"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.1640625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="11.125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
     <col min="2" max="2" width="3" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" customWidth="1"/>
-    <col min="4" max="4" width="21.1640625" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" customWidth="1"/>
+    <col min="3" max="3" width="14.625" customWidth="1"/>
+    <col min="4" max="4" width="21.125" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
     <col min="6" max="6" width="6.5" customWidth="1"/>
     <col min="7" max="7" width="3.5" customWidth="1"/>
     <col min="8" max="8" width="5" customWidth="1"/>
-    <col min="9" max="11" width="4.83203125" customWidth="1"/>
+    <col min="9" max="11" width="4.875" customWidth="1"/>
     <col min="12" max="12" width="4.5" customWidth="1"/>
     <col min="13" max="13" width="8.5" customWidth="1"/>
-    <col min="14" max="17" width="4.33203125" customWidth="1"/>
-    <col min="18" max="19" width="3.6640625" customWidth="1"/>
+    <col min="14" max="17" width="4.375" customWidth="1"/>
+    <col min="18" max="19" width="3.625" customWidth="1"/>
     <col min="20" max="20" width="6.5" customWidth="1"/>
-    <col min="21" max="26" width="3.6640625" customWidth="1"/>
+    <col min="21" max="26" width="3.625" customWidth="1"/>
     <col min="27" max="27" width="4.5" customWidth="1"/>
-    <col min="28" max="30" width="3.6640625" customWidth="1"/>
+    <col min="28" max="30" width="3.625" customWidth="1"/>
     <col min="31" max="31" width="6.5" customWidth="1"/>
     <col min="32" max="32" width="1" customWidth="1"/>
-    <col min="33" max="33" width="6.6640625" customWidth="1"/>
-    <col min="34" max="34" width="8.1640625" customWidth="1"/>
-    <col min="35" max="38" width="9.33203125" customWidth="1"/>
-    <col min="39" max="39" width="0.6640625" customWidth="1"/>
-    <col min="40" max="40" width="36.1640625" customWidth="1"/>
+    <col min="33" max="33" width="6.625" customWidth="1"/>
+    <col min="34" max="34" width="8.125" customWidth="1"/>
+    <col min="35" max="38" width="9.375" customWidth="1"/>
+    <col min="39" max="39" width="0.625" customWidth="1"/>
+    <col min="40" max="40" width="36.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="15.75" customHeight="1">
@@ -1472,52 +1471,52 @@
     <row r="3" spans="1:40" ht="44.25" customHeight="1">
       <c r="A3" s="9"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="97" t="s">
+      <c r="C3" s="92" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="94"/>
-      <c r="E3" s="98" t="s">
+      <c r="D3" s="89"/>
+      <c r="E3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="99" t="s">
+      <c r="F3" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="100" t="s">
+      <c r="G3" s="95" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="101" t="s">
+      <c r="H3" s="96" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="102"/>
-      <c r="J3" s="102"/>
-      <c r="K3" s="102"/>
-      <c r="L3" s="103"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="97"/>
+      <c r="K3" s="97"/>
+      <c r="L3" s="98"/>
       <c r="M3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="104" t="s">
+      <c r="N3" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="O3" s="102"/>
-      <c r="P3" s="102"/>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="102"/>
-      <c r="S3" s="103"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="98"/>
       <c r="T3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="U3" s="105" t="s">
+      <c r="U3" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="V3" s="102"/>
-      <c r="W3" s="102"/>
-      <c r="X3" s="102"/>
-      <c r="Y3" s="102"/>
-      <c r="Z3" s="102"/>
-      <c r="AA3" s="102"/>
-      <c r="AB3" s="102"/>
-      <c r="AC3" s="102"/>
-      <c r="AD3" s="103"/>
+      <c r="V3" s="97"/>
+      <c r="W3" s="97"/>
+      <c r="X3" s="97"/>
+      <c r="Y3" s="97"/>
+      <c r="Z3" s="97"/>
+      <c r="AA3" s="97"/>
+      <c r="AB3" s="97"/>
+      <c r="AC3" s="97"/>
+      <c r="AD3" s="98"/>
       <c r="AE3" s="13" t="s">
         <v>6</v>
       </c>
@@ -1525,17 +1524,17 @@
       <c r="AG3" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AH3" s="90" t="s">
+      <c r="AH3" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="AI3" s="92" t="s">
+      <c r="AI3" s="87" t="s">
         <v>10</v>
       </c>
-      <c r="AJ3" s="93"/>
-      <c r="AK3" s="93"/>
-      <c r="AL3" s="94"/>
+      <c r="AJ3" s="88"/>
+      <c r="AK3" s="88"/>
+      <c r="AL3" s="89"/>
       <c r="AM3" s="4"/>
-      <c r="AN3" s="95" t="s">
+      <c r="AN3" s="90" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1550,9 +1549,9 @@
       <c r="D4" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="96"/>
-      <c r="F4" s="96"/>
-      <c r="G4" s="96"/>
+      <c r="E4" s="91"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="91"/>
       <c r="H4" s="17" t="s">
         <v>15</v>
       </c>
@@ -1630,7 +1629,7 @@
         <f t="shared" ref="AG4:AG14" si="0">SUM(M4,T4,AE4)</f>
         <v>21</v>
       </c>
-      <c r="AH4" s="91"/>
+      <c r="AH4" s="86"/>
       <c r="AI4" s="29" t="s">
         <v>34</v>
       </c>
@@ -1644,7 +1643,7 @@
         <v>37</v>
       </c>
       <c r="AM4" s="4"/>
-      <c r="AN4" s="96"/>
+      <c r="AN4" s="91"/>
     </row>
     <row r="5" spans="1:40" ht="15.75" customHeight="1">
       <c r="A5" s="9" t="s">
@@ -1662,67 +1661,67 @@
       <c r="E5" s="31">
         <v>1860101</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G5" s="9">
         <v>1</v>
       </c>
-      <c r="H5" s="33">
+      <c r="H5" s="32">
         <v>3</v>
       </c>
-      <c r="I5" s="34"/>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34">
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32">
         <f t="shared" ref="M5:M14" si="1">SUM(H5:L5)</f>
         <v>3</v>
       </c>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="36">
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="34">
         <f t="shared" ref="T5:T14" si="2">SUM(N5:S5)</f>
         <v>0</v>
       </c>
-      <c r="U5" s="37"/>
-      <c r="V5" s="37"/>
-      <c r="W5" s="37"/>
-      <c r="X5" s="37"/>
-      <c r="Y5" s="37"/>
-      <c r="Z5" s="37"/>
-      <c r="AA5" s="37"/>
-      <c r="AB5" s="37"/>
-      <c r="AC5" s="37"/>
-      <c r="AD5" s="37"/>
-      <c r="AE5" s="38">
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+      <c r="X5" s="35"/>
+      <c r="Y5" s="35"/>
+      <c r="Z5" s="35"/>
+      <c r="AA5" s="35"/>
+      <c r="AB5" s="35"/>
+      <c r="AC5" s="35"/>
+      <c r="AD5" s="35"/>
+      <c r="AE5" s="36">
         <f t="shared" ref="AE5:AE14" si="3">SUM(U5:AD5)</f>
         <v>0</v>
       </c>
-      <c r="AF5" s="39"/>
-      <c r="AG5" s="40">
+      <c r="AF5" s="37"/>
+      <c r="AG5" s="38">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="42" t="s">
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="AJ5" s="43"/>
-      <c r="AK5" s="43"/>
-      <c r="AL5" s="43"/>
+      <c r="AJ5" s="40"/>
+      <c r="AK5" s="40"/>
+      <c r="AL5" s="40"/>
       <c r="AM5" s="4"/>
-      <c r="AN5" s="44"/>
+      <c r="AN5" s="41"/>
     </row>
     <row r="6" spans="1:40" ht="15.75" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="44">
+      <c r="B6" s="41">
         <v>2</v>
       </c>
       <c r="C6" s="30" t="s">
@@ -1734,65 +1733,65 @@
       <c r="E6" s="31">
         <v>1860270</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="F6" s="9" t="s">
         <v>45</v>
       </c>
       <c r="G6" s="9">
         <v>1</v>
       </c>
-      <c r="H6" s="33">
+      <c r="H6" s="32">
         <v>3</v>
       </c>
-      <c r="I6" s="34"/>
-      <c r="J6" s="34"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34">
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="36">
+      <c r="N6" s="33"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="33"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="33"/>
+      <c r="S6" s="33"/>
+      <c r="T6" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U6" s="37"/>
-      <c r="V6" s="45">
+      <c r="U6" s="35"/>
+      <c r="V6" s="35">
         <v>3</v>
       </c>
-      <c r="W6" s="45">
+      <c r="W6" s="35">
         <v>3</v>
       </c>
-      <c r="X6" s="37"/>
-      <c r="Y6" s="45">
+      <c r="X6" s="35"/>
+      <c r="Y6" s="35">
         <v>3</v>
       </c>
-      <c r="Z6" s="37"/>
-      <c r="AA6" s="37"/>
-      <c r="AB6" s="37"/>
-      <c r="AC6" s="37"/>
-      <c r="AD6" s="37"/>
-      <c r="AE6" s="38">
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="35"/>
+      <c r="AC6" s="35"/>
+      <c r="AD6" s="35"/>
+      <c r="AE6" s="36">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="AF6" s="39"/>
-      <c r="AG6" s="40">
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="38">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="43"/>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="43"/>
-      <c r="AL6" s="43"/>
+      <c r="AH6" s="39"/>
+      <c r="AI6" s="40"/>
+      <c r="AJ6" s="40"/>
+      <c r="AK6" s="40"/>
+      <c r="AL6" s="40"/>
       <c r="AM6" s="4"/>
-      <c r="AN6" s="44"/>
+      <c r="AN6" s="41"/>
     </row>
     <row r="7" spans="1:40" ht="15.75" customHeight="1">
       <c r="A7" s="9" t="s">
@@ -1810,75 +1809,75 @@
       <c r="E7" s="31">
         <v>1860271</v>
       </c>
-      <c r="F7" s="32" t="s">
+      <c r="F7" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="9">
         <v>1</v>
       </c>
-      <c r="H7" s="33">
+      <c r="H7" s="32">
         <v>3</v>
       </c>
-      <c r="I7" s="33">
+      <c r="I7" s="32">
         <v>3</v>
       </c>
-      <c r="J7" s="33">
+      <c r="J7" s="32">
         <v>3</v>
       </c>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34">
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="N7" s="35"/>
-      <c r="O7" s="46">
+      <c r="N7" s="33"/>
+      <c r="O7" s="33">
         <v>3</v>
       </c>
-      <c r="P7" s="46">
+      <c r="P7" s="33">
         <v>3</v>
       </c>
-      <c r="Q7" s="46">
+      <c r="Q7" s="33">
         <v>3</v>
       </c>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="36">
+      <c r="R7" s="33"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="34">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="U7" s="37"/>
-      <c r="V7" s="45">
+      <c r="U7" s="35"/>
+      <c r="V7" s="35">
         <v>3</v>
       </c>
-      <c r="W7" s="45">
+      <c r="W7" s="35">
         <v>3</v>
       </c>
-      <c r="X7" s="37"/>
-      <c r="Y7" s="45">
+      <c r="X7" s="35"/>
+      <c r="Y7" s="35">
         <v>3</v>
       </c>
-      <c r="Z7" s="37"/>
-      <c r="AA7" s="37"/>
-      <c r="AB7" s="37"/>
-      <c r="AC7" s="37"/>
-      <c r="AD7" s="37"/>
-      <c r="AE7" s="38">
+      <c r="Z7" s="35"/>
+      <c r="AA7" s="35"/>
+      <c r="AB7" s="35"/>
+      <c r="AC7" s="35"/>
+      <c r="AD7" s="35"/>
+      <c r="AE7" s="36">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="AF7" s="39"/>
-      <c r="AG7" s="40">
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="38">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="AH7" s="41"/>
-      <c r="AI7" s="43"/>
-      <c r="AJ7" s="43"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="43"/>
+      <c r="AH7" s="39"/>
+      <c r="AI7" s="40"/>
+      <c r="AJ7" s="40"/>
+      <c r="AK7" s="40"/>
+      <c r="AL7" s="40"/>
       <c r="AM7" s="4"/>
-      <c r="AN7" s="44"/>
+      <c r="AN7" s="41"/>
     </row>
     <row r="8" spans="1:40" ht="15.75" customHeight="1">
       <c r="A8" s="9" t="s">
@@ -1896,79 +1895,79 @@
       <c r="E8" s="31">
         <v>1860272</v>
       </c>
-      <c r="F8" s="32" t="s">
+      <c r="F8" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G8" s="9">
         <v>1</v>
       </c>
-      <c r="H8" s="33">
+      <c r="H8" s="32">
         <v>3</v>
       </c>
-      <c r="I8" s="33">
+      <c r="I8" s="32">
         <v>3</v>
       </c>
-      <c r="J8" s="33">
+      <c r="J8" s="32">
         <v>3</v>
       </c>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34">
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="N8" s="35"/>
-      <c r="O8" s="46">
+      <c r="N8" s="33"/>
+      <c r="O8" s="33">
         <v>3</v>
       </c>
-      <c r="P8" s="46">
+      <c r="P8" s="33">
         <v>3</v>
       </c>
-      <c r="Q8" s="46">
+      <c r="Q8" s="33">
         <v>3</v>
       </c>
-      <c r="R8" s="35"/>
-      <c r="S8" s="47"/>
-      <c r="T8" s="36">
+      <c r="R8" s="33"/>
+      <c r="S8" s="42"/>
+      <c r="T8" s="34">
         <f t="shared" si="2"/>
         <v>9</v>
       </c>
-      <c r="U8" s="37"/>
-      <c r="V8" s="45">
+      <c r="U8" s="35"/>
+      <c r="V8" s="35">
         <v>3</v>
       </c>
-      <c r="W8" s="37"/>
-      <c r="X8" s="37"/>
-      <c r="Y8" s="45">
+      <c r="W8" s="35"/>
+      <c r="X8" s="35"/>
+      <c r="Y8" s="35">
         <v>3</v>
       </c>
-      <c r="Z8" s="45"/>
-      <c r="AA8" s="48"/>
-      <c r="AB8" s="37"/>
-      <c r="AC8" s="37"/>
-      <c r="AD8" s="37"/>
-      <c r="AE8" s="38">
+      <c r="Z8" s="35"/>
+      <c r="AA8" s="43"/>
+      <c r="AB8" s="35"/>
+      <c r="AC8" s="35"/>
+      <c r="AD8" s="35"/>
+      <c r="AE8" s="36">
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="AF8" s="39"/>
-      <c r="AG8" s="40">
+      <c r="AF8" s="37"/>
+      <c r="AG8" s="38">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="AH8" s="41"/>
-      <c r="AI8" s="43"/>
-      <c r="AJ8" s="43"/>
-      <c r="AK8" s="43"/>
-      <c r="AL8" s="43"/>
+      <c r="AH8" s="39"/>
+      <c r="AI8" s="40"/>
+      <c r="AJ8" s="40"/>
+      <c r="AK8" s="40"/>
+      <c r="AL8" s="40"/>
       <c r="AM8" s="4"/>
-      <c r="AN8" s="44"/>
+      <c r="AN8" s="41"/>
     </row>
     <row r="9" spans="1:40" ht="15.75" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="44">
+      <c r="B9" s="41">
         <v>5</v>
       </c>
       <c r="C9" s="30" t="s">
@@ -1980,73 +1979,73 @@
       <c r="E9" s="31">
         <v>1860283</v>
       </c>
-      <c r="F9" s="32" t="s">
+      <c r="F9" s="9" t="s">
         <v>45</v>
       </c>
       <c r="G9" s="9">
         <v>1</v>
       </c>
-      <c r="H9" s="34"/>
-      <c r="I9" s="34"/>
-      <c r="J9" s="34"/>
-      <c r="K9" s="34"/>
-      <c r="L9" s="34"/>
-      <c r="M9" s="34">
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N9" s="35"/>
-      <c r="O9" s="46">
+      <c r="N9" s="33"/>
+      <c r="O9" s="33">
         <v>3</v>
       </c>
-      <c r="P9" s="46">
+      <c r="P9" s="33">
         <v>3</v>
       </c>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="36">
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="U9" s="37"/>
-      <c r="V9" s="45">
+      <c r="U9" s="35"/>
+      <c r="V9" s="35">
         <v>3</v>
       </c>
-      <c r="W9" s="45">
+      <c r="W9" s="35">
         <v>3</v>
       </c>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="45">
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35">
         <v>3</v>
       </c>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="38">
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AD9" s="35"/>
+      <c r="AE9" s="36">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="40">
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="43"/>
-      <c r="AJ9" s="43"/>
-      <c r="AK9" s="43"/>
-      <c r="AL9" s="43"/>
+      <c r="AH9" s="39"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="40"/>
+      <c r="AK9" s="40"/>
+      <c r="AL9" s="40"/>
       <c r="AM9" s="4"/>
-      <c r="AN9" s="44"/>
+      <c r="AN9" s="41"/>
     </row>
     <row r="10" spans="1:40" ht="15.75" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="44">
+      <c r="B10" s="41">
         <v>6</v>
       </c>
       <c r="C10" s="30" t="s">
@@ -2058,73 +2057,73 @@
       <c r="E10" s="31">
         <v>1860291</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G10" s="9">
         <v>1</v>
       </c>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="34"/>
-      <c r="K10" s="34"/>
-      <c r="L10" s="34"/>
-      <c r="M10" s="34">
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N10" s="35"/>
-      <c r="O10" s="46">
+      <c r="N10" s="33"/>
+      <c r="O10" s="33">
         <v>3</v>
       </c>
-      <c r="P10" s="46">
+      <c r="P10" s="33">
         <v>3</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="36">
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="U10" s="37"/>
-      <c r="V10" s="45">
+      <c r="U10" s="35"/>
+      <c r="V10" s="35">
         <v>3</v>
       </c>
-      <c r="W10" s="45">
+      <c r="W10" s="35">
         <v>3</v>
       </c>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="45">
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35">
         <v>3</v>
       </c>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37"/>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="38">
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="36">
         <f t="shared" si="3"/>
         <v>9</v>
       </c>
-      <c r="AF10" s="39"/>
-      <c r="AG10" s="40">
+      <c r="AF10" s="37"/>
+      <c r="AG10" s="38">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="43"/>
-      <c r="AJ10" s="43"/>
-      <c r="AK10" s="43"/>
-      <c r="AL10" s="43"/>
+      <c r="AH10" s="39"/>
+      <c r="AI10" s="40"/>
+      <c r="AJ10" s="40"/>
+      <c r="AK10" s="40"/>
+      <c r="AL10" s="40"/>
       <c r="AM10" s="4"/>
-      <c r="AN10" s="44"/>
+      <c r="AN10" s="41"/>
     </row>
     <row r="11" spans="1:40" ht="15.75" customHeight="1">
       <c r="A11" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="44">
+      <c r="B11" s="41">
         <v>7</v>
       </c>
       <c r="C11" s="30" t="s">
@@ -2136,67 +2135,67 @@
       <c r="E11" s="31">
         <v>1860050</v>
       </c>
-      <c r="F11" s="32" t="s">
+      <c r="F11" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G11" s="9">
         <v>2</v>
       </c>
-      <c r="H11" s="34"/>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="34"/>
-      <c r="L11" s="34"/>
-      <c r="M11" s="34">
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N11" s="35"/>
-      <c r="O11" s="46">
+      <c r="N11" s="33"/>
+      <c r="O11" s="33">
         <v>3</v>
       </c>
-      <c r="P11" s="46">
+      <c r="P11" s="33">
         <v>3</v>
       </c>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="36">
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="U11" s="37"/>
-      <c r="V11" s="37"/>
-      <c r="W11" s="37"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="37"/>
-      <c r="Z11" s="37"/>
-      <c r="AA11" s="37"/>
-      <c r="AB11" s="37"/>
-      <c r="AC11" s="37"/>
-      <c r="AD11" s="37"/>
-      <c r="AE11" s="38">
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+      <c r="X11" s="35"/>
+      <c r="Y11" s="35"/>
+      <c r="Z11" s="35"/>
+      <c r="AA11" s="35"/>
+      <c r="AB11" s="35"/>
+      <c r="AC11" s="35"/>
+      <c r="AD11" s="35"/>
+      <c r="AE11" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF11" s="39"/>
-      <c r="AG11" s="40">
+      <c r="AF11" s="37"/>
+      <c r="AG11" s="38">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="43"/>
-      <c r="AJ11" s="43"/>
-      <c r="AK11" s="43"/>
-      <c r="AL11" s="43"/>
+      <c r="AH11" s="39"/>
+      <c r="AI11" s="40"/>
+      <c r="AJ11" s="40"/>
+      <c r="AK11" s="40"/>
+      <c r="AL11" s="40"/>
       <c r="AM11" s="4"/>
-      <c r="AN11" s="44"/>
+      <c r="AN11" s="41"/>
     </row>
     <row r="12" spans="1:40" ht="15.75" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="44">
+      <c r="B12" s="41">
         <v>8</v>
       </c>
       <c r="C12" s="30" t="s">
@@ -2208,67 +2207,67 @@
       <c r="E12" s="31">
         <v>1860051</v>
       </c>
-      <c r="F12" s="32" t="s">
+      <c r="F12" s="9" t="s">
         <v>45</v>
       </c>
       <c r="G12" s="9">
         <v>2</v>
       </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="34"/>
-      <c r="J12" s="34"/>
-      <c r="K12" s="34"/>
-      <c r="L12" s="34"/>
-      <c r="M12" s="34">
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N12" s="35"/>
-      <c r="O12" s="46">
+      <c r="N12" s="33"/>
+      <c r="O12" s="33">
         <v>3</v>
       </c>
-      <c r="P12" s="46">
+      <c r="P12" s="33">
         <v>3</v>
       </c>
-      <c r="Q12" s="35"/>
-      <c r="R12" s="35"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="36">
+      <c r="Q12" s="33"/>
+      <c r="R12" s="33"/>
+      <c r="S12" s="33"/>
+      <c r="T12" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="U12" s="37"/>
-      <c r="V12" s="37"/>
-      <c r="W12" s="37"/>
-      <c r="X12" s="37"/>
-      <c r="Y12" s="37"/>
-      <c r="Z12" s="37"/>
-      <c r="AA12" s="37"/>
-      <c r="AB12" s="37"/>
-      <c r="AC12" s="37"/>
-      <c r="AD12" s="37"/>
-      <c r="AE12" s="38">
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+      <c r="X12" s="35"/>
+      <c r="Y12" s="35"/>
+      <c r="Z12" s="35"/>
+      <c r="AA12" s="35"/>
+      <c r="AB12" s="35"/>
+      <c r="AC12" s="35"/>
+      <c r="AD12" s="35"/>
+      <c r="AE12" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="40">
+      <c r="AF12" s="37"/>
+      <c r="AG12" s="38">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="43"/>
-      <c r="AJ12" s="43"/>
-      <c r="AK12" s="43"/>
-      <c r="AL12" s="43"/>
+      <c r="AH12" s="39"/>
+      <c r="AI12" s="40"/>
+      <c r="AJ12" s="40"/>
+      <c r="AK12" s="40"/>
+      <c r="AL12" s="40"/>
       <c r="AM12" s="4"/>
-      <c r="AN12" s="44"/>
+      <c r="AN12" s="41"/>
     </row>
     <row r="13" spans="1:40" ht="15.75" customHeight="1">
       <c r="A13" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="44">
+      <c r="B13" s="41">
         <v>9</v>
       </c>
       <c r="C13" s="30" t="s">
@@ -2280,240 +2279,240 @@
       <c r="E13" s="31">
         <v>1860154</v>
       </c>
-      <c r="F13" s="32" t="s">
+      <c r="F13" s="9" t="s">
         <v>41</v>
       </c>
       <c r="G13" s="9">
         <v>2</v>
       </c>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="34"/>
-      <c r="L13" s="34"/>
-      <c r="M13" s="34">
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N13" s="35"/>
-      <c r="O13" s="46">
+      <c r="N13" s="33"/>
+      <c r="O13" s="33">
         <v>3</v>
       </c>
-      <c r="P13" s="46">
+      <c r="P13" s="33">
         <v>3</v>
       </c>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="36">
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33"/>
+      <c r="S13" s="33"/>
+      <c r="T13" s="34">
         <f t="shared" si="2"/>
         <v>6</v>
       </c>
-      <c r="U13" s="37"/>
-      <c r="V13" s="37"/>
-      <c r="W13" s="37"/>
-      <c r="X13" s="37"/>
-      <c r="Y13" s="37"/>
-      <c r="Z13" s="37"/>
-      <c r="AA13" s="37"/>
-      <c r="AB13" s="37"/>
-      <c r="AC13" s="37"/>
-      <c r="AD13" s="37"/>
-      <c r="AE13" s="38">
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+      <c r="X13" s="35"/>
+      <c r="Y13" s="35"/>
+      <c r="Z13" s="35"/>
+      <c r="AA13" s="35"/>
+      <c r="AB13" s="35"/>
+      <c r="AC13" s="35"/>
+      <c r="AD13" s="35"/>
+      <c r="AE13" s="36">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF13" s="39"/>
-      <c r="AG13" s="40">
+      <c r="AF13" s="37"/>
+      <c r="AG13" s="38">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="43"/>
-      <c r="AJ13" s="43"/>
-      <c r="AK13" s="43"/>
-      <c r="AL13" s="43"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="40"/>
+      <c r="AJ13" s="40"/>
+      <c r="AK13" s="40"/>
+      <c r="AL13" s="40"/>
       <c r="AM13" s="4"/>
-      <c r="AN13" s="44"/>
+      <c r="AN13" s="41"/>
     </row>
     <row r="14" spans="1:40" ht="15.75" customHeight="1">
       <c r="A14" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="49">
+      <c r="B14" s="44">
         <v>10</v>
       </c>
-      <c r="C14" s="50" t="s">
+      <c r="C14" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="49" t="s">
+      <c r="D14" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="E14" s="51">
+      <c r="E14" s="46">
         <v>1860179</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="52">
+      <c r="G14" s="47">
         <v>2</v>
       </c>
-      <c r="H14" s="53"/>
-      <c r="I14" s="53"/>
-      <c r="J14" s="53"/>
-      <c r="K14" s="53"/>
-      <c r="L14" s="53"/>
-      <c r="M14" s="53">
+      <c r="H14" s="48"/>
+      <c r="I14" s="48"/>
+      <c r="J14" s="48"/>
+      <c r="K14" s="48"/>
+      <c r="L14" s="48"/>
+      <c r="M14" s="48">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="N14" s="54"/>
-      <c r="O14" s="54"/>
-      <c r="P14" s="54"/>
-      <c r="Q14" s="54"/>
-      <c r="R14" s="54"/>
-      <c r="S14" s="54"/>
-      <c r="T14" s="55">
+      <c r="N14" s="49"/>
+      <c r="O14" s="49"/>
+      <c r="P14" s="49"/>
+      <c r="Q14" s="49"/>
+      <c r="R14" s="49"/>
+      <c r="S14" s="49"/>
+      <c r="T14" s="50">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="U14" s="56"/>
-      <c r="V14" s="56"/>
-      <c r="W14" s="56"/>
-      <c r="X14" s="56"/>
-      <c r="Y14" s="56"/>
-      <c r="Z14" s="56"/>
-      <c r="AA14" s="56"/>
-      <c r="AB14" s="56"/>
-      <c r="AC14" s="56"/>
-      <c r="AD14" s="56"/>
-      <c r="AE14" s="57">
+      <c r="U14" s="51"/>
+      <c r="V14" s="51"/>
+      <c r="W14" s="51"/>
+      <c r="X14" s="51"/>
+      <c r="Y14" s="51"/>
+      <c r="Z14" s="51"/>
+      <c r="AA14" s="51"/>
+      <c r="AB14" s="51"/>
+      <c r="AC14" s="51"/>
+      <c r="AD14" s="51"/>
+      <c r="AE14" s="52">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="AF14" s="58"/>
-      <c r="AG14" s="59">
+      <c r="AF14" s="53"/>
+      <c r="AG14" s="54">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="AH14" s="60"/>
-      <c r="AI14" s="61"/>
-      <c r="AJ14" s="61"/>
-      <c r="AK14" s="61"/>
-      <c r="AL14" s="61"/>
+      <c r="AH14" s="55"/>
+      <c r="AI14" s="56"/>
+      <c r="AJ14" s="56"/>
+      <c r="AK14" s="56"/>
+      <c r="AL14" s="56"/>
       <c r="AM14" s="4"/>
-      <c r="AN14" s="44"/>
+      <c r="AN14" s="41"/>
     </row>
     <row r="15" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="67"/>
-      <c r="I15" s="67"/>
-      <c r="J15" s="67"/>
-      <c r="K15" s="67"/>
-      <c r="L15" s="67"/>
-      <c r="M15" s="67"/>
-      <c r="N15" s="67"/>
-      <c r="O15" s="67"/>
-      <c r="P15" s="67"/>
-      <c r="Q15" s="67"/>
-      <c r="R15" s="67"/>
-      <c r="S15" s="67"/>
-      <c r="T15" s="68"/>
-      <c r="U15" s="67"/>
-      <c r="V15" s="67"/>
-      <c r="W15" s="67"/>
-      <c r="X15" s="67"/>
-      <c r="Y15" s="67"/>
-      <c r="Z15" s="67"/>
-      <c r="AA15" s="67"/>
-      <c r="AB15" s="67"/>
-      <c r="AC15" s="67"/>
-      <c r="AD15" s="67"/>
-      <c r="AE15" s="68"/>
-      <c r="AF15" s="68"/>
-      <c r="AG15" s="68"/>
-      <c r="AH15" s="69"/>
-      <c r="AI15" s="70"/>
-      <c r="AJ15" s="70"/>
-      <c r="AK15" s="70"/>
-      <c r="AL15" s="71"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="62"/>
+      <c r="I15" s="62"/>
+      <c r="J15" s="62"/>
+      <c r="K15" s="62"/>
+      <c r="L15" s="62"/>
+      <c r="M15" s="62"/>
+      <c r="N15" s="62"/>
+      <c r="O15" s="62"/>
+      <c r="P15" s="62"/>
+      <c r="Q15" s="62"/>
+      <c r="R15" s="62"/>
+      <c r="S15" s="62"/>
+      <c r="T15" s="63"/>
+      <c r="U15" s="62"/>
+      <c r="V15" s="62"/>
+      <c r="W15" s="62"/>
+      <c r="X15" s="62"/>
+      <c r="Y15" s="62"/>
+      <c r="Z15" s="62"/>
+      <c r="AA15" s="62"/>
+      <c r="AB15" s="62"/>
+      <c r="AC15" s="62"/>
+      <c r="AD15" s="62"/>
+      <c r="AE15" s="63"/>
+      <c r="AF15" s="63"/>
+      <c r="AG15" s="63"/>
+      <c r="AH15" s="64"/>
+      <c r="AI15" s="65"/>
+      <c r="AJ15" s="65"/>
+      <c r="AK15" s="65"/>
+      <c r="AL15" s="66"/>
       <c r="AM15" s="4"/>
       <c r="AN15" s="4"/>
     </row>
     <row r="16" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A16" s="72" t="s">
+      <c r="A16" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B16" s="73">
+      <c r="B16" s="68">
         <v>1</v>
       </c>
-      <c r="C16" s="74" t="s">
+      <c r="C16" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="74" t="s">
+      <c r="D16" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="E16" s="75">
+      <c r="E16" s="70">
         <v>1960211</v>
       </c>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72">
+      <c r="F16" s="67"/>
+      <c r="G16" s="67">
         <v>1</v>
       </c>
-      <c r="H16" s="76"/>
-      <c r="I16" s="76"/>
-      <c r="J16" s="76"/>
-      <c r="K16" s="76"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="76">
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71">
         <f t="shared" ref="M16:M26" si="4">SUM(H16:L16)</f>
         <v>0</v>
       </c>
-      <c r="N16" s="77"/>
-      <c r="O16" s="77"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="77"/>
-      <c r="T16" s="79">
+      <c r="N16" s="72"/>
+      <c r="O16" s="72"/>
+      <c r="P16" s="72"/>
+      <c r="Q16" s="72"/>
+      <c r="R16" s="73"/>
+      <c r="S16" s="72"/>
+      <c r="T16" s="74">
         <f t="shared" ref="T16:T26" si="5">SUM(N16:S16)</f>
         <v>0</v>
       </c>
-      <c r="U16" s="80"/>
-      <c r="V16" s="80"/>
-      <c r="W16" s="80"/>
-      <c r="X16" s="80"/>
-      <c r="Y16" s="80"/>
-      <c r="Z16" s="80"/>
-      <c r="AA16" s="80"/>
-      <c r="AB16" s="80"/>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="80"/>
-      <c r="AE16" s="81">
+      <c r="U16" s="75"/>
+      <c r="V16" s="75"/>
+      <c r="W16" s="75"/>
+      <c r="X16" s="75"/>
+      <c r="Y16" s="75"/>
+      <c r="Z16" s="75"/>
+      <c r="AA16" s="75"/>
+      <c r="AB16" s="75"/>
+      <c r="AC16" s="75"/>
+      <c r="AD16" s="75"/>
+      <c r="AE16" s="76">
         <f t="shared" ref="AE16:AE26" si="6">SUM(U16:AD16)</f>
         <v>0</v>
       </c>
-      <c r="AF16" s="82"/>
-      <c r="AG16" s="83">
+      <c r="AF16" s="77"/>
+      <c r="AG16" s="78">
         <f t="shared" ref="AG16:AG26" si="7">SUM(M16,T16,AE16)</f>
         <v>0</v>
       </c>
-      <c r="AH16" s="84"/>
-      <c r="AI16" s="85"/>
-      <c r="AJ16" s="85"/>
-      <c r="AK16" s="85"/>
-      <c r="AL16" s="85"/>
+      <c r="AH16" s="79"/>
+      <c r="AI16" s="80"/>
+      <c r="AJ16" s="80"/>
+      <c r="AK16" s="80"/>
+      <c r="AL16" s="80"/>
       <c r="AM16" s="4"/>
-      <c r="AN16" s="44"/>
+      <c r="AN16" s="41"/>
     </row>
     <row r="17" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A17" s="72" t="s">
+      <c r="A17" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B17" s="16">
@@ -2532,54 +2531,54 @@
       <c r="G17" s="9">
         <v>1</v>
       </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34">
+      <c r="H17" s="32"/>
+      <c r="I17" s="32"/>
+      <c r="J17" s="32"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N17" s="35"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="36">
+      <c r="N17" s="33"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U17" s="37"/>
-      <c r="V17" s="37"/>
-      <c r="W17" s="37"/>
-      <c r="X17" s="37"/>
-      <c r="Y17" s="37"/>
-      <c r="Z17" s="37"/>
-      <c r="AA17" s="37"/>
-      <c r="AB17" s="37"/>
-      <c r="AC17" s="37"/>
-      <c r="AD17" s="37"/>
-      <c r="AE17" s="38">
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+      <c r="X17" s="35"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="35"/>
+      <c r="AA17" s="35"/>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="35"/>
+      <c r="AD17" s="35"/>
+      <c r="AE17" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF17" s="39"/>
-      <c r="AG17" s="40">
+      <c r="AF17" s="37"/>
+      <c r="AG17" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH17" s="41"/>
-      <c r="AI17" s="43"/>
-      <c r="AJ17" s="43"/>
-      <c r="AK17" s="43"/>
-      <c r="AL17" s="43"/>
+      <c r="AH17" s="39"/>
+      <c r="AI17" s="40"/>
+      <c r="AJ17" s="40"/>
+      <c r="AK17" s="40"/>
+      <c r="AL17" s="40"/>
       <c r="AM17" s="4"/>
-      <c r="AN17" s="44"/>
+      <c r="AN17" s="41"/>
     </row>
     <row r="18" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A18" s="72" t="s">
+      <c r="A18" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B18" s="16">
@@ -2598,57 +2597,57 @@
       <c r="G18" s="9">
         <v>1</v>
       </c>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34">
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N18" s="35"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="36">
+      <c r="N18" s="33"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U18" s="37"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="37"/>
-      <c r="X18" s="37"/>
-      <c r="Y18" s="37"/>
-      <c r="Z18" s="37"/>
-      <c r="AA18" s="37"/>
-      <c r="AB18" s="37"/>
-      <c r="AC18" s="37"/>
-      <c r="AD18" s="37"/>
-      <c r="AE18" s="38">
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+      <c r="X18" s="35"/>
+      <c r="Y18" s="35"/>
+      <c r="Z18" s="35"/>
+      <c r="AA18" s="35"/>
+      <c r="AB18" s="35"/>
+      <c r="AC18" s="35"/>
+      <c r="AD18" s="35"/>
+      <c r="AE18" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF18" s="39"/>
-      <c r="AG18" s="40">
+      <c r="AF18" s="37"/>
+      <c r="AG18" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH18" s="41"/>
-      <c r="AI18" s="43"/>
-      <c r="AJ18" s="43"/>
-      <c r="AK18" s="43"/>
-      <c r="AL18" s="43"/>
+      <c r="AH18" s="39"/>
+      <c r="AI18" s="40"/>
+      <c r="AJ18" s="40"/>
+      <c r="AK18" s="40"/>
+      <c r="AL18" s="40"/>
       <c r="AM18" s="4"/>
-      <c r="AN18" s="44"/>
+      <c r="AN18" s="41"/>
     </row>
     <row r="19" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B19" s="44">
+      <c r="B19" s="41">
         <v>4</v>
       </c>
       <c r="C19" s="30" t="s">
@@ -2662,57 +2661,57 @@
       <c r="G19" s="9">
         <v>1</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34">
+      <c r="H19" s="32"/>
+      <c r="I19" s="32"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="32"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N19" s="35"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="36">
+      <c r="N19" s="33"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U19" s="37"/>
-      <c r="V19" s="37"/>
-      <c r="W19" s="37"/>
-      <c r="X19" s="37"/>
-      <c r="Y19" s="37"/>
-      <c r="Z19" s="37"/>
-      <c r="AA19" s="37"/>
-      <c r="AB19" s="37"/>
-      <c r="AC19" s="37"/>
-      <c r="AD19" s="37"/>
-      <c r="AE19" s="38">
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+      <c r="X19" s="35"/>
+      <c r="Y19" s="35"/>
+      <c r="Z19" s="35"/>
+      <c r="AA19" s="35"/>
+      <c r="AB19" s="35"/>
+      <c r="AC19" s="35"/>
+      <c r="AD19" s="35"/>
+      <c r="AE19" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF19" s="39"/>
-      <c r="AG19" s="40">
+      <c r="AF19" s="37"/>
+      <c r="AG19" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="43"/>
-      <c r="AJ19" s="43"/>
-      <c r="AK19" s="43"/>
-      <c r="AL19" s="43"/>
+      <c r="AH19" s="39"/>
+      <c r="AI19" s="40"/>
+      <c r="AJ19" s="40"/>
+      <c r="AK19" s="40"/>
+      <c r="AL19" s="40"/>
       <c r="AM19" s="4"/>
-      <c r="AN19" s="44"/>
+      <c r="AN19" s="41"/>
     </row>
     <row r="20" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A20" s="72" t="s">
+      <c r="A20" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B20" s="44">
+      <c r="B20" s="41">
         <v>5</v>
       </c>
       <c r="C20" s="30" t="s">
@@ -2728,57 +2727,57 @@
       <c r="G20" s="9">
         <v>1</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34">
+      <c r="H20" s="32"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N20" s="35"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="36">
+      <c r="N20" s="33"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33"/>
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U20" s="37"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="37"/>
-      <c r="X20" s="37"/>
-      <c r="Y20" s="37"/>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="37"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="37"/>
-      <c r="AD20" s="37"/>
-      <c r="AE20" s="38">
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+      <c r="X20" s="35"/>
+      <c r="Y20" s="35"/>
+      <c r="Z20" s="35"/>
+      <c r="AA20" s="35"/>
+      <c r="AB20" s="35"/>
+      <c r="AC20" s="35"/>
+      <c r="AD20" s="35"/>
+      <c r="AE20" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF20" s="39"/>
-      <c r="AG20" s="40">
+      <c r="AF20" s="37"/>
+      <c r="AG20" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="43"/>
-      <c r="AJ20" s="43"/>
-      <c r="AK20" s="43"/>
-      <c r="AL20" s="43"/>
+      <c r="AH20" s="39"/>
+      <c r="AI20" s="40"/>
+      <c r="AJ20" s="40"/>
+      <c r="AK20" s="40"/>
+      <c r="AL20" s="40"/>
       <c r="AM20" s="4"/>
-      <c r="AN20" s="44"/>
+      <c r="AN20" s="41"/>
     </row>
     <row r="21" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A21" s="72" t="s">
+      <c r="A21" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B21" s="44">
+      <c r="B21" s="41">
         <v>6</v>
       </c>
       <c r="C21" s="30" t="s">
@@ -2794,57 +2793,57 @@
       <c r="G21" s="9">
         <v>1</v>
       </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
-      <c r="K21" s="34"/>
-      <c r="L21" s="34"/>
-      <c r="M21" s="34">
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N21" s="35"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="36">
+      <c r="N21" s="33"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U21" s="37"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="37"/>
-      <c r="X21" s="37"/>
-      <c r="Y21" s="37"/>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="38">
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+      <c r="X21" s="35"/>
+      <c r="Y21" s="35"/>
+      <c r="Z21" s="35"/>
+      <c r="AA21" s="35"/>
+      <c r="AB21" s="35"/>
+      <c r="AC21" s="35"/>
+      <c r="AD21" s="35"/>
+      <c r="AE21" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF21" s="39"/>
-      <c r="AG21" s="40">
+      <c r="AF21" s="37"/>
+      <c r="AG21" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="43"/>
-      <c r="AJ21" s="43"/>
-      <c r="AK21" s="43"/>
-      <c r="AL21" s="43"/>
+      <c r="AH21" s="39"/>
+      <c r="AI21" s="40"/>
+      <c r="AJ21" s="40"/>
+      <c r="AK21" s="40"/>
+      <c r="AL21" s="40"/>
       <c r="AM21" s="4"/>
-      <c r="AN21" s="44"/>
+      <c r="AN21" s="41"/>
     </row>
     <row r="22" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A22" s="72" t="s">
+      <c r="A22" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="B22" s="44">
+      <c r="B22" s="41">
         <v>7</v>
       </c>
       <c r="C22" s="30" t="s">
@@ -2860,54 +2859,54 @@
       <c r="G22" s="9">
         <v>1</v>
       </c>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34">
+      <c r="H22" s="32"/>
+      <c r="I22" s="32"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="32"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N22" s="35"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35"/>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="36">
+      <c r="N22" s="33"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U22" s="37"/>
-      <c r="V22" s="37"/>
-      <c r="W22" s="37"/>
-      <c r="X22" s="37"/>
-      <c r="Y22" s="37"/>
-      <c r="Z22" s="37"/>
-      <c r="AA22" s="37"/>
-      <c r="AB22" s="37"/>
-      <c r="AC22" s="37"/>
-      <c r="AD22" s="37"/>
-      <c r="AE22" s="38">
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
+      <c r="AA22" s="35"/>
+      <c r="AB22" s="35"/>
+      <c r="AC22" s="35"/>
+      <c r="AD22" s="35"/>
+      <c r="AE22" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF22" s="39"/>
-      <c r="AG22" s="40">
+      <c r="AF22" s="37"/>
+      <c r="AG22" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH22" s="41"/>
-      <c r="AI22" s="43"/>
-      <c r="AJ22" s="43"/>
-      <c r="AK22" s="43"/>
-      <c r="AL22" s="43"/>
+      <c r="AH22" s="39"/>
+      <c r="AI22" s="40"/>
+      <c r="AJ22" s="40"/>
+      <c r="AK22" s="40"/>
+      <c r="AL22" s="40"/>
       <c r="AM22" s="4"/>
-      <c r="AN22" s="44"/>
+      <c r="AN22" s="41"/>
     </row>
     <row r="23" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A23" s="72" t="s">
+      <c r="A23" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B23" s="16">
@@ -2926,54 +2925,54 @@
       <c r="G23" s="9">
         <v>1</v>
       </c>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34">
+      <c r="H23" s="32"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N23" s="35"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="36">
+      <c r="N23" s="33"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U23" s="37"/>
-      <c r="V23" s="37"/>
-      <c r="W23" s="37"/>
-      <c r="X23" s="37"/>
-      <c r="Y23" s="37"/>
-      <c r="Z23" s="37"/>
-      <c r="AA23" s="37"/>
-      <c r="AB23" s="37"/>
-      <c r="AC23" s="37"/>
-      <c r="AD23" s="37"/>
-      <c r="AE23" s="38">
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+      <c r="X23" s="35"/>
+      <c r="Y23" s="35"/>
+      <c r="Z23" s="35"/>
+      <c r="AA23" s="35"/>
+      <c r="AB23" s="35"/>
+      <c r="AC23" s="35"/>
+      <c r="AD23" s="35"/>
+      <c r="AE23" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF23" s="39"/>
-      <c r="AG23" s="40">
+      <c r="AF23" s="37"/>
+      <c r="AG23" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH23" s="41"/>
-      <c r="AI23" s="43"/>
-      <c r="AJ23" s="43"/>
-      <c r="AK23" s="43"/>
-      <c r="AL23" s="43"/>
+      <c r="AH23" s="39"/>
+      <c r="AI23" s="40"/>
+      <c r="AJ23" s="40"/>
+      <c r="AK23" s="40"/>
+      <c r="AL23" s="40"/>
       <c r="AM23" s="4"/>
-      <c r="AN23" s="44"/>
+      <c r="AN23" s="41"/>
     </row>
     <row r="24" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B24" s="16">
@@ -2992,54 +2991,54 @@
       <c r="G24" s="9">
         <v>1</v>
       </c>
-      <c r="H24" s="34"/>
-      <c r="I24" s="34"/>
-      <c r="J24" s="34"/>
-      <c r="K24" s="34"/>
-      <c r="L24" s="34"/>
-      <c r="M24" s="34">
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N24" s="35"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35"/>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="36">
+      <c r="N24" s="33"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U24" s="37"/>
-      <c r="V24" s="37"/>
-      <c r="W24" s="37"/>
-      <c r="X24" s="37"/>
-      <c r="Y24" s="37"/>
-      <c r="Z24" s="37"/>
-      <c r="AA24" s="37"/>
-      <c r="AB24" s="37"/>
-      <c r="AC24" s="37"/>
-      <c r="AD24" s="37"/>
-      <c r="AE24" s="38">
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+      <c r="X24" s="35"/>
+      <c r="Y24" s="35"/>
+      <c r="Z24" s="35"/>
+      <c r="AA24" s="35"/>
+      <c r="AB24" s="35"/>
+      <c r="AC24" s="35"/>
+      <c r="AD24" s="35"/>
+      <c r="AE24" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF24" s="39"/>
-      <c r="AG24" s="40">
+      <c r="AF24" s="37"/>
+      <c r="AG24" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="43"/>
-      <c r="AJ24" s="43"/>
-      <c r="AK24" s="43"/>
-      <c r="AL24" s="43"/>
+      <c r="AH24" s="39"/>
+      <c r="AI24" s="40"/>
+      <c r="AJ24" s="40"/>
+      <c r="AK24" s="40"/>
+      <c r="AL24" s="40"/>
       <c r="AM24" s="4"/>
-      <c r="AN24" s="44"/>
+      <c r="AN24" s="41"/>
     </row>
     <row r="25" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A25" s="72" t="s">
+      <c r="A25" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B25" s="16">
@@ -3058,54 +3057,54 @@
       <c r="G25" s="9">
         <v>1</v>
       </c>
-      <c r="H25" s="34"/>
-      <c r="I25" s="34"/>
-      <c r="J25" s="34"/>
-      <c r="K25" s="34"/>
-      <c r="L25" s="34"/>
-      <c r="M25" s="34">
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="32"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="36">
+      <c r="N25" s="33"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U25" s="37"/>
-      <c r="V25" s="37"/>
-      <c r="W25" s="37"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="37"/>
-      <c r="Z25" s="37"/>
-      <c r="AA25" s="37"/>
-      <c r="AB25" s="37"/>
-      <c r="AC25" s="37"/>
-      <c r="AD25" s="37"/>
-      <c r="AE25" s="38">
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="35"/>
+      <c r="AC25" s="35"/>
+      <c r="AD25" s="35"/>
+      <c r="AE25" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF25" s="39"/>
-      <c r="AG25" s="40">
+      <c r="AF25" s="37"/>
+      <c r="AG25" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH25" s="41"/>
-      <c r="AI25" s="43"/>
-      <c r="AJ25" s="43"/>
-      <c r="AK25" s="43"/>
-      <c r="AL25" s="43"/>
+      <c r="AH25" s="39"/>
+      <c r="AI25" s="40"/>
+      <c r="AJ25" s="40"/>
+      <c r="AK25" s="40"/>
+      <c r="AL25" s="40"/>
       <c r="AM25" s="4"/>
-      <c r="AN25" s="44"/>
+      <c r="AN25" s="41"/>
     </row>
     <row r="26" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A26" s="72" t="s">
+      <c r="A26" s="67" t="s">
         <v>62</v>
       </c>
       <c r="B26" s="16">
@@ -3124,91 +3123,91 @@
       <c r="G26" s="9">
         <v>1</v>
       </c>
-      <c r="H26" s="34"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="34"/>
-      <c r="K26" s="34"/>
-      <c r="L26" s="34"/>
-      <c r="M26" s="34">
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="N26" s="35"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="36">
+      <c r="N26" s="33"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="34">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="U26" s="37"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="37"/>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="37"/>
-      <c r="AB26" s="37"/>
-      <c r="AC26" s="37"/>
-      <c r="AD26" s="37"/>
-      <c r="AE26" s="38">
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="35"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="AF26" s="39"/>
-      <c r="AG26" s="40">
+      <c r="AF26" s="37"/>
+      <c r="AG26" s="38">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="43"/>
-      <c r="AJ26" s="43"/>
-      <c r="AK26" s="43"/>
-      <c r="AL26" s="43"/>
+      <c r="AH26" s="39"/>
+      <c r="AI26" s="40"/>
+      <c r="AJ26" s="40"/>
+      <c r="AK26" s="40"/>
+      <c r="AL26" s="40"/>
       <c r="AM26" s="4"/>
-      <c r="AN26" s="44"/>
+      <c r="AN26" s="41"/>
     </row>
     <row r="27" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A27" s="62"/>
-      <c r="B27" s="63"/>
-      <c r="C27" s="64"/>
-      <c r="D27" s="64"/>
-      <c r="E27" s="65"/>
-      <c r="F27" s="66"/>
-      <c r="G27" s="66"/>
-      <c r="H27" s="67"/>
-      <c r="I27" s="67"/>
-      <c r="J27" s="67"/>
-      <c r="K27" s="67"/>
-      <c r="L27" s="67"/>
-      <c r="M27" s="67"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="67"/>
-      <c r="P27" s="67"/>
-      <c r="Q27" s="67"/>
-      <c r="R27" s="67"/>
-      <c r="S27" s="67"/>
-      <c r="T27" s="68"/>
-      <c r="U27" s="67"/>
-      <c r="V27" s="67"/>
-      <c r="W27" s="67"/>
-      <c r="X27" s="67"/>
-      <c r="Y27" s="67"/>
-      <c r="Z27" s="67"/>
-      <c r="AA27" s="67"/>
-      <c r="AB27" s="67"/>
-      <c r="AC27" s="67"/>
-      <c r="AD27" s="67"/>
-      <c r="AE27" s="68"/>
-      <c r="AF27" s="68"/>
-      <c r="AG27" s="68"/>
-      <c r="AH27" s="69"/>
-      <c r="AI27" s="70"/>
-      <c r="AJ27" s="70"/>
-      <c r="AK27" s="70"/>
-      <c r="AL27" s="71"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="62"/>
+      <c r="L27" s="62"/>
+      <c r="M27" s="62"/>
+      <c r="N27" s="62"/>
+      <c r="O27" s="62"/>
+      <c r="P27" s="62"/>
+      <c r="Q27" s="62"/>
+      <c r="R27" s="62"/>
+      <c r="S27" s="62"/>
+      <c r="T27" s="63"/>
+      <c r="U27" s="62"/>
+      <c r="V27" s="62"/>
+      <c r="W27" s="62"/>
+      <c r="X27" s="62"/>
+      <c r="Y27" s="62"/>
+      <c r="Z27" s="62"/>
+      <c r="AA27" s="62"/>
+      <c r="AB27" s="62"/>
+      <c r="AC27" s="62"/>
+      <c r="AD27" s="62"/>
+      <c r="AE27" s="63"/>
+      <c r="AF27" s="63"/>
+      <c r="AG27" s="63"/>
+      <c r="AH27" s="64"/>
+      <c r="AI27" s="65"/>
+      <c r="AJ27" s="65"/>
+      <c r="AK27" s="65"/>
+      <c r="AL27" s="66"/>
       <c r="AM27" s="4"/>
       <c r="AN27" s="4"/>
     </row>
@@ -3232,51 +3231,51 @@
       <c r="G28" s="9">
         <v>2</v>
       </c>
-      <c r="H28" s="34"/>
-      <c r="I28" s="34"/>
-      <c r="J28" s="34"/>
-      <c r="K28" s="34"/>
-      <c r="L28" s="34"/>
-      <c r="M28" s="34">
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32">
         <f t="shared" ref="M28:M42" si="8">SUM(H28:L28)</f>
         <v>0</v>
       </c>
-      <c r="N28" s="35"/>
-      <c r="O28" s="35"/>
-      <c r="P28" s="35"/>
-      <c r="Q28" s="35"/>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="36">
+      <c r="N28" s="33"/>
+      <c r="O28" s="33"/>
+      <c r="P28" s="33"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="34">
         <f t="shared" ref="T28:T42" si="9">SUM(N28:S28)</f>
         <v>0</v>
       </c>
-      <c r="U28" s="37"/>
-      <c r="V28" s="37"/>
-      <c r="W28" s="37"/>
-      <c r="X28" s="37"/>
-      <c r="Y28" s="37"/>
-      <c r="Z28" s="37"/>
-      <c r="AA28" s="37"/>
-      <c r="AB28" s="37"/>
-      <c r="AC28" s="37"/>
-      <c r="AD28" s="37"/>
-      <c r="AE28" s="38">
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
+      <c r="AA28" s="35"/>
+      <c r="AB28" s="35"/>
+      <c r="AC28" s="35"/>
+      <c r="AD28" s="35"/>
+      <c r="AE28" s="36">
         <f t="shared" ref="AE28:AE42" si="10">SUM(U28:AD28)</f>
         <v>0</v>
       </c>
-      <c r="AF28" s="39"/>
-      <c r="AG28" s="40">
+      <c r="AF28" s="37"/>
+      <c r="AG28" s="38">
         <f t="shared" ref="AG28:AG42" si="11">SUM(M28,T28,AE28)</f>
         <v>0</v>
       </c>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="43"/>
-      <c r="AJ28" s="43"/>
-      <c r="AK28" s="43"/>
-      <c r="AL28" s="43"/>
+      <c r="AH28" s="39"/>
+      <c r="AI28" s="40"/>
+      <c r="AJ28" s="40"/>
+      <c r="AK28" s="40"/>
+      <c r="AL28" s="40"/>
       <c r="AM28" s="4"/>
-      <c r="AN28" s="44"/>
+      <c r="AN28" s="41"/>
     </row>
     <row r="29" spans="1:40" ht="15.75" customHeight="1">
       <c r="A29" s="9" t="s">
@@ -3299,51 +3298,51 @@
       <c r="G29" s="9">
         <v>2</v>
       </c>
-      <c r="H29" s="34"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
-      <c r="L29" s="34"/>
-      <c r="M29" s="34">
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N29" s="35"/>
-      <c r="O29" s="35"/>
-      <c r="P29" s="35"/>
-      <c r="Q29" s="35"/>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="36">
+      <c r="N29" s="33"/>
+      <c r="O29" s="33"/>
+      <c r="P29" s="33"/>
+      <c r="Q29" s="33"/>
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U29" s="37"/>
-      <c r="V29" s="37"/>
-      <c r="W29" s="37"/>
-      <c r="X29" s="37"/>
-      <c r="Y29" s="37"/>
-      <c r="Z29" s="37"/>
-      <c r="AA29" s="37"/>
-      <c r="AB29" s="37"/>
-      <c r="AC29" s="37"/>
-      <c r="AD29" s="37"/>
-      <c r="AE29" s="38">
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+      <c r="X29" s="35"/>
+      <c r="Y29" s="35"/>
+      <c r="Z29" s="35"/>
+      <c r="AA29" s="35"/>
+      <c r="AB29" s="35"/>
+      <c r="AC29" s="35"/>
+      <c r="AD29" s="35"/>
+      <c r="AE29" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="40">
+      <c r="AF29" s="37"/>
+      <c r="AG29" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH29" s="41"/>
-      <c r="AI29" s="43"/>
-      <c r="AJ29" s="43"/>
-      <c r="AK29" s="43"/>
-      <c r="AL29" s="43"/>
+      <c r="AH29" s="39"/>
+      <c r="AI29" s="40"/>
+      <c r="AJ29" s="40"/>
+      <c r="AK29" s="40"/>
+      <c r="AL29" s="40"/>
       <c r="AM29" s="4"/>
-      <c r="AN29" s="44"/>
+      <c r="AN29" s="41"/>
     </row>
     <row r="30" spans="1:40" ht="15.75" customHeight="1">
       <c r="A30" s="9" t="s">
@@ -3366,51 +3365,51 @@
       <c r="G30" s="9">
         <v>2</v>
       </c>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="34">
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
+      <c r="J30" s="32"/>
+      <c r="K30" s="32"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N30" s="35"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35"/>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="36">
+      <c r="N30" s="33"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33"/>
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U30" s="37"/>
-      <c r="V30" s="37"/>
-      <c r="W30" s="37"/>
-      <c r="X30" s="37"/>
-      <c r="Y30" s="37"/>
-      <c r="Z30" s="37"/>
-      <c r="AA30" s="37"/>
-      <c r="AB30" s="37"/>
-      <c r="AC30" s="37"/>
-      <c r="AD30" s="37"/>
-      <c r="AE30" s="38">
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+      <c r="X30" s="35"/>
+      <c r="Y30" s="35"/>
+      <c r="Z30" s="35"/>
+      <c r="AA30" s="35"/>
+      <c r="AB30" s="35"/>
+      <c r="AC30" s="35"/>
+      <c r="AD30" s="35"/>
+      <c r="AE30" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF30" s="39"/>
-      <c r="AG30" s="40">
+      <c r="AF30" s="37"/>
+      <c r="AG30" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH30" s="41"/>
-      <c r="AI30" s="43"/>
-      <c r="AJ30" s="43"/>
-      <c r="AK30" s="43"/>
-      <c r="AL30" s="43"/>
+      <c r="AH30" s="39"/>
+      <c r="AI30" s="40"/>
+      <c r="AJ30" s="40"/>
+      <c r="AK30" s="40"/>
+      <c r="AL30" s="40"/>
       <c r="AM30" s="4"/>
-      <c r="AN30" s="44"/>
+      <c r="AN30" s="41"/>
     </row>
     <row r="31" spans="1:40" ht="15.75" customHeight="1">
       <c r="A31" s="9" t="s">
@@ -3433,51 +3432,51 @@
       <c r="G31" s="9">
         <v>2</v>
       </c>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34">
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
+      <c r="J31" s="32"/>
+      <c r="K31" s="32"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="36">
+      <c r="N31" s="33"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U31" s="37"/>
-      <c r="V31" s="37"/>
-      <c r="W31" s="37"/>
-      <c r="X31" s="37"/>
-      <c r="Y31" s="37"/>
-      <c r="Z31" s="37"/>
-      <c r="AA31" s="37"/>
-      <c r="AB31" s="37"/>
-      <c r="AC31" s="37"/>
-      <c r="AD31" s="37"/>
-      <c r="AE31" s="38">
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
+      <c r="AA31" s="35"/>
+      <c r="AB31" s="35"/>
+      <c r="AC31" s="35"/>
+      <c r="AD31" s="35"/>
+      <c r="AE31" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF31" s="39"/>
-      <c r="AG31" s="40">
+      <c r="AF31" s="37"/>
+      <c r="AG31" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH31" s="41"/>
-      <c r="AI31" s="43"/>
-      <c r="AJ31" s="43"/>
-      <c r="AK31" s="43"/>
-      <c r="AL31" s="43"/>
+      <c r="AH31" s="39"/>
+      <c r="AI31" s="40"/>
+      <c r="AJ31" s="40"/>
+      <c r="AK31" s="40"/>
+      <c r="AL31" s="40"/>
       <c r="AM31" s="4"/>
-      <c r="AN31" s="44"/>
+      <c r="AN31" s="41"/>
     </row>
     <row r="32" spans="1:40" ht="15.75" customHeight="1">
       <c r="A32" s="9" t="s">
@@ -3500,51 +3499,51 @@
       <c r="G32" s="9">
         <v>2</v>
       </c>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34">
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
+      <c r="J32" s="32"/>
+      <c r="K32" s="32"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N32" s="35"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="36">
+      <c r="N32" s="33"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33"/>
+      <c r="S32" s="33"/>
+      <c r="T32" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U32" s="37"/>
-      <c r="V32" s="37"/>
-      <c r="W32" s="37"/>
-      <c r="X32" s="37"/>
-      <c r="Y32" s="37"/>
-      <c r="Z32" s="37"/>
-      <c r="AA32" s="37"/>
-      <c r="AB32" s="37"/>
-      <c r="AC32" s="37"/>
-      <c r="AD32" s="37"/>
-      <c r="AE32" s="38">
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+      <c r="X32" s="35"/>
+      <c r="Y32" s="35"/>
+      <c r="Z32" s="35"/>
+      <c r="AA32" s="35"/>
+      <c r="AB32" s="35"/>
+      <c r="AC32" s="35"/>
+      <c r="AD32" s="35"/>
+      <c r="AE32" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF32" s="39"/>
-      <c r="AG32" s="40">
+      <c r="AF32" s="37"/>
+      <c r="AG32" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH32" s="41"/>
-      <c r="AI32" s="43"/>
-      <c r="AJ32" s="43"/>
-      <c r="AK32" s="43"/>
-      <c r="AL32" s="43"/>
+      <c r="AH32" s="39"/>
+      <c r="AI32" s="40"/>
+      <c r="AJ32" s="40"/>
+      <c r="AK32" s="40"/>
+      <c r="AL32" s="40"/>
       <c r="AM32" s="4"/>
-      <c r="AN32" s="44"/>
+      <c r="AN32" s="41"/>
     </row>
     <row r="33" spans="1:40" ht="15.75" customHeight="1">
       <c r="A33" s="9" t="s">
@@ -3567,51 +3566,51 @@
       <c r="G33" s="9">
         <v>2</v>
       </c>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34">
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+      <c r="K33" s="32"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N33" s="35"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="36">
+      <c r="N33" s="33"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U33" s="37"/>
-      <c r="V33" s="37"/>
-      <c r="W33" s="37"/>
-      <c r="X33" s="37"/>
-      <c r="Y33" s="37"/>
-      <c r="Z33" s="37"/>
-      <c r="AA33" s="37"/>
-      <c r="AB33" s="37"/>
-      <c r="AC33" s="37"/>
-      <c r="AD33" s="37"/>
-      <c r="AE33" s="38">
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35"/>
+      <c r="X33" s="35"/>
+      <c r="Y33" s="35"/>
+      <c r="Z33" s="35"/>
+      <c r="AA33" s="35"/>
+      <c r="AB33" s="35"/>
+      <c r="AC33" s="35"/>
+      <c r="AD33" s="35"/>
+      <c r="AE33" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF33" s="39"/>
-      <c r="AG33" s="40">
+      <c r="AF33" s="37"/>
+      <c r="AG33" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH33" s="41"/>
-      <c r="AI33" s="43"/>
-      <c r="AJ33" s="43"/>
-      <c r="AK33" s="43"/>
-      <c r="AL33" s="43"/>
+      <c r="AH33" s="39"/>
+      <c r="AI33" s="40"/>
+      <c r="AJ33" s="40"/>
+      <c r="AK33" s="40"/>
+      <c r="AL33" s="40"/>
       <c r="AM33" s="4"/>
-      <c r="AN33" s="44"/>
+      <c r="AN33" s="41"/>
     </row>
     <row r="34" spans="1:40" ht="15.75" customHeight="1">
       <c r="A34" s="9" t="s">
@@ -3634,51 +3633,51 @@
       <c r="G34" s="9">
         <v>2</v>
       </c>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34">
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
+      <c r="J34" s="32"/>
+      <c r="K34" s="32"/>
+      <c r="L34" s="32"/>
+      <c r="M34" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N34" s="35"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="36">
+      <c r="N34" s="33"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U34" s="37"/>
-      <c r="V34" s="37"/>
-      <c r="W34" s="37"/>
-      <c r="X34" s="37"/>
-      <c r="Y34" s="37"/>
-      <c r="Z34" s="37"/>
-      <c r="AA34" s="37"/>
-      <c r="AB34" s="37"/>
-      <c r="AC34" s="37"/>
-      <c r="AD34" s="37"/>
-      <c r="AE34" s="38">
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35"/>
+      <c r="X34" s="35"/>
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35"/>
+      <c r="AA34" s="35"/>
+      <c r="AB34" s="35"/>
+      <c r="AC34" s="35"/>
+      <c r="AD34" s="35"/>
+      <c r="AE34" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF34" s="39"/>
-      <c r="AG34" s="40">
+      <c r="AF34" s="37"/>
+      <c r="AG34" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH34" s="41"/>
-      <c r="AI34" s="43"/>
-      <c r="AJ34" s="43"/>
-      <c r="AK34" s="43"/>
-      <c r="AL34" s="43"/>
+      <c r="AH34" s="39"/>
+      <c r="AI34" s="40"/>
+      <c r="AJ34" s="40"/>
+      <c r="AK34" s="40"/>
+      <c r="AL34" s="40"/>
       <c r="AM34" s="4"/>
-      <c r="AN34" s="44"/>
+      <c r="AN34" s="41"/>
     </row>
     <row r="35" spans="1:40" ht="15.75" customHeight="1">
       <c r="A35" s="9" t="s">
@@ -3701,51 +3700,51 @@
       <c r="G35" s="9">
         <v>2</v>
       </c>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34">
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N35" s="35"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35"/>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="36">
+      <c r="N35" s="33"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33"/>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U35" s="37"/>
-      <c r="V35" s="37"/>
-      <c r="W35" s="37"/>
-      <c r="X35" s="37"/>
-      <c r="Y35" s="37"/>
-      <c r="Z35" s="37"/>
-      <c r="AA35" s="37"/>
-      <c r="AB35" s="37"/>
-      <c r="AC35" s="37"/>
-      <c r="AD35" s="37"/>
-      <c r="AE35" s="38">
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+      <c r="X35" s="35"/>
+      <c r="Y35" s="35"/>
+      <c r="Z35" s="35"/>
+      <c r="AA35" s="35"/>
+      <c r="AB35" s="35"/>
+      <c r="AC35" s="35"/>
+      <c r="AD35" s="35"/>
+      <c r="AE35" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF35" s="39"/>
-      <c r="AG35" s="40">
+      <c r="AF35" s="37"/>
+      <c r="AG35" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH35" s="41"/>
-      <c r="AI35" s="43"/>
-      <c r="AJ35" s="43"/>
-      <c r="AK35" s="43"/>
-      <c r="AL35" s="43"/>
+      <c r="AH35" s="39"/>
+      <c r="AI35" s="40"/>
+      <c r="AJ35" s="40"/>
+      <c r="AK35" s="40"/>
+      <c r="AL35" s="40"/>
       <c r="AM35" s="4"/>
-      <c r="AN35" s="44"/>
+      <c r="AN35" s="41"/>
     </row>
     <row r="36" spans="1:40" ht="15.75" customHeight="1">
       <c r="A36" s="9" t="s">
@@ -3768,51 +3767,51 @@
       <c r="G36" s="9">
         <v>2</v>
       </c>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34">
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
+      <c r="J36" s="32"/>
+      <c r="K36" s="32"/>
+      <c r="L36" s="32"/>
+      <c r="M36" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N36" s="35"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35"/>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="36">
+      <c r="N36" s="33"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33"/>
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U36" s="37"/>
-      <c r="V36" s="37"/>
-      <c r="W36" s="37"/>
-      <c r="X36" s="37"/>
-      <c r="Y36" s="37"/>
-      <c r="Z36" s="37"/>
-      <c r="AA36" s="37"/>
-      <c r="AB36" s="37"/>
-      <c r="AC36" s="37"/>
-      <c r="AD36" s="37"/>
-      <c r="AE36" s="38">
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
+      <c r="AA36" s="35"/>
+      <c r="AB36" s="35"/>
+      <c r="AC36" s="35"/>
+      <c r="AD36" s="35"/>
+      <c r="AE36" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF36" s="39"/>
-      <c r="AG36" s="40">
+      <c r="AF36" s="37"/>
+      <c r="AG36" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH36" s="41"/>
-      <c r="AI36" s="43"/>
-      <c r="AJ36" s="43"/>
-      <c r="AK36" s="43"/>
-      <c r="AL36" s="43"/>
+      <c r="AH36" s="39"/>
+      <c r="AI36" s="40"/>
+      <c r="AJ36" s="40"/>
+      <c r="AK36" s="40"/>
+      <c r="AL36" s="40"/>
       <c r="AM36" s="4"/>
-      <c r="AN36" s="44"/>
+      <c r="AN36" s="41"/>
     </row>
     <row r="37" spans="1:40" ht="15.75" customHeight="1">
       <c r="A37" s="9" t="s">
@@ -3835,51 +3834,51 @@
       <c r="G37" s="9">
         <v>2</v>
       </c>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34">
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
+      <c r="L37" s="32"/>
+      <c r="M37" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N37" s="35"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35"/>
-      <c r="T37" s="36">
+      <c r="N37" s="33"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33"/>
+      <c r="T37" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U37" s="37"/>
-      <c r="V37" s="37"/>
-      <c r="W37" s="37"/>
-      <c r="X37" s="37"/>
-      <c r="Y37" s="37"/>
-      <c r="Z37" s="37"/>
-      <c r="AA37" s="37"/>
-      <c r="AB37" s="37"/>
-      <c r="AC37" s="37"/>
-      <c r="AD37" s="37"/>
-      <c r="AE37" s="38">
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="35"/>
+      <c r="X37" s="35"/>
+      <c r="Y37" s="35"/>
+      <c r="Z37" s="35"/>
+      <c r="AA37" s="35"/>
+      <c r="AB37" s="35"/>
+      <c r="AC37" s="35"/>
+      <c r="AD37" s="35"/>
+      <c r="AE37" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF37" s="39"/>
-      <c r="AG37" s="40">
+      <c r="AF37" s="37"/>
+      <c r="AG37" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH37" s="41"/>
-      <c r="AI37" s="43"/>
-      <c r="AJ37" s="43"/>
-      <c r="AK37" s="43"/>
-      <c r="AL37" s="43"/>
+      <c r="AH37" s="39"/>
+      <c r="AI37" s="40"/>
+      <c r="AJ37" s="40"/>
+      <c r="AK37" s="40"/>
+      <c r="AL37" s="40"/>
       <c r="AM37" s="4"/>
-      <c r="AN37" s="44"/>
+      <c r="AN37" s="41"/>
     </row>
     <row r="38" spans="1:40" ht="15.75" customHeight="1">
       <c r="A38" s="9" t="s">
@@ -3902,51 +3901,51 @@
       <c r="G38" s="9">
         <v>2</v>
       </c>
-      <c r="H38" s="34"/>
-      <c r="I38" s="34"/>
-      <c r="J38" s="34"/>
-      <c r="K38" s="34"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="34">
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
+      <c r="M38" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N38" s="35"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35"/>
-      <c r="R38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="36">
+      <c r="N38" s="33"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33"/>
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U38" s="37"/>
-      <c r="V38" s="37"/>
-      <c r="W38" s="37"/>
-      <c r="X38" s="37"/>
-      <c r="Y38" s="37"/>
-      <c r="Z38" s="37"/>
-      <c r="AA38" s="37"/>
-      <c r="AB38" s="37"/>
-      <c r="AC38" s="37"/>
-      <c r="AD38" s="37"/>
-      <c r="AE38" s="38">
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+      <c r="X38" s="35"/>
+      <c r="Y38" s="35"/>
+      <c r="Z38" s="35"/>
+      <c r="AA38" s="35"/>
+      <c r="AB38" s="35"/>
+      <c r="AC38" s="35"/>
+      <c r="AD38" s="35"/>
+      <c r="AE38" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF38" s="39"/>
-      <c r="AG38" s="40">
+      <c r="AF38" s="37"/>
+      <c r="AG38" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH38" s="41"/>
-      <c r="AI38" s="43"/>
-      <c r="AJ38" s="43"/>
-      <c r="AK38" s="43"/>
-      <c r="AL38" s="43"/>
+      <c r="AH38" s="39"/>
+      <c r="AI38" s="40"/>
+      <c r="AJ38" s="40"/>
+      <c r="AK38" s="40"/>
+      <c r="AL38" s="40"/>
       <c r="AM38" s="4"/>
-      <c r="AN38" s="44"/>
+      <c r="AN38" s="41"/>
     </row>
     <row r="39" spans="1:40" ht="15.75" customHeight="1">
       <c r="A39" s="9" t="s">
@@ -3969,51 +3968,51 @@
       <c r="G39" s="9">
         <v>2</v>
       </c>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34">
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
+      <c r="M39" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N39" s="35"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="35"/>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="36">
+      <c r="N39" s="33"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="37"/>
-      <c r="X39" s="37"/>
-      <c r="Y39" s="37"/>
-      <c r="Z39" s="37"/>
-      <c r="AA39" s="37"/>
-      <c r="AB39" s="37"/>
-      <c r="AC39" s="37"/>
-      <c r="AD39" s="37"/>
-      <c r="AE39" s="38">
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
+      <c r="AA39" s="35"/>
+      <c r="AB39" s="35"/>
+      <c r="AC39" s="35"/>
+      <c r="AD39" s="35"/>
+      <c r="AE39" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF39" s="39"/>
-      <c r="AG39" s="40">
+      <c r="AF39" s="37"/>
+      <c r="AG39" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH39" s="41"/>
-      <c r="AI39" s="43"/>
-      <c r="AJ39" s="43"/>
-      <c r="AK39" s="43"/>
-      <c r="AL39" s="43"/>
+      <c r="AH39" s="39"/>
+      <c r="AI39" s="40"/>
+      <c r="AJ39" s="40"/>
+      <c r="AK39" s="40"/>
+      <c r="AL39" s="40"/>
       <c r="AM39" s="4"/>
-      <c r="AN39" s="44"/>
+      <c r="AN39" s="41"/>
     </row>
     <row r="40" spans="1:40" ht="15.75" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -4036,51 +4035,51 @@
       <c r="G40" s="9">
         <v>2</v>
       </c>
-      <c r="H40" s="34"/>
-      <c r="I40" s="34"/>
-      <c r="J40" s="34"/>
-      <c r="K40" s="34"/>
-      <c r="L40" s="34"/>
-      <c r="M40" s="34">
+      <c r="H40" s="32"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
+      <c r="L40" s="32"/>
+      <c r="M40" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N40" s="35"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="35"/>
-      <c r="S40" s="35"/>
-      <c r="T40" s="36">
+      <c r="N40" s="33"/>
+      <c r="O40" s="33"/>
+      <c r="P40" s="33"/>
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U40" s="37"/>
-      <c r="V40" s="37"/>
-      <c r="W40" s="37"/>
-      <c r="X40" s="37"/>
-      <c r="Y40" s="37"/>
-      <c r="Z40" s="37"/>
-      <c r="AA40" s="37"/>
-      <c r="AB40" s="37"/>
-      <c r="AC40" s="37"/>
-      <c r="AD40" s="37"/>
-      <c r="AE40" s="38">
+      <c r="U40" s="35"/>
+      <c r="V40" s="35"/>
+      <c r="W40" s="35"/>
+      <c r="X40" s="35"/>
+      <c r="Y40" s="35"/>
+      <c r="Z40" s="35"/>
+      <c r="AA40" s="35"/>
+      <c r="AB40" s="35"/>
+      <c r="AC40" s="35"/>
+      <c r="AD40" s="35"/>
+      <c r="AE40" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF40" s="39"/>
-      <c r="AG40" s="40">
+      <c r="AF40" s="37"/>
+      <c r="AG40" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH40" s="41"/>
-      <c r="AI40" s="43"/>
-      <c r="AJ40" s="43"/>
-      <c r="AK40" s="43"/>
-      <c r="AL40" s="43"/>
+      <c r="AH40" s="39"/>
+      <c r="AI40" s="40"/>
+      <c r="AJ40" s="40"/>
+      <c r="AK40" s="40"/>
+      <c r="AL40" s="40"/>
       <c r="AM40" s="4"/>
-      <c r="AN40" s="44"/>
+      <c r="AN40" s="41"/>
     </row>
     <row r="41" spans="1:40" ht="15.75" customHeight="1">
       <c r="A41" s="9" t="s">
@@ -4102,57 +4101,57 @@
       <c r="G41" s="9">
         <v>2</v>
       </c>
-      <c r="H41" s="34"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
-      <c r="K41" s="34"/>
-      <c r="L41" s="34"/>
-      <c r="M41" s="34">
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+      <c r="M41" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N41" s="35"/>
-      <c r="O41" s="35"/>
-      <c r="P41" s="35"/>
-      <c r="Q41" s="35"/>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="36">
+      <c r="N41" s="33"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33"/>
+      <c r="Q41" s="33"/>
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U41" s="37"/>
-      <c r="V41" s="37"/>
-      <c r="W41" s="37"/>
-      <c r="X41" s="37"/>
-      <c r="Y41" s="37"/>
-      <c r="Z41" s="37"/>
-      <c r="AA41" s="37"/>
-      <c r="AB41" s="37"/>
-      <c r="AC41" s="37"/>
-      <c r="AD41" s="37"/>
-      <c r="AE41" s="38">
+      <c r="U41" s="35"/>
+      <c r="V41" s="35"/>
+      <c r="W41" s="35"/>
+      <c r="X41" s="35"/>
+      <c r="Y41" s="35"/>
+      <c r="Z41" s="35"/>
+      <c r="AA41" s="35"/>
+      <c r="AB41" s="35"/>
+      <c r="AC41" s="35"/>
+      <c r="AD41" s="35"/>
+      <c r="AE41" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF41" s="39"/>
-      <c r="AG41" s="40">
+      <c r="AF41" s="37"/>
+      <c r="AG41" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH41" s="41"/>
-      <c r="AI41" s="43"/>
-      <c r="AJ41" s="43"/>
-      <c r="AK41" s="43"/>
-      <c r="AL41" s="43"/>
+      <c r="AH41" s="39"/>
+      <c r="AI41" s="40"/>
+      <c r="AJ41" s="40"/>
+      <c r="AK41" s="40"/>
+      <c r="AL41" s="40"/>
       <c r="AM41" s="4"/>
-      <c r="AN41" s="44"/>
+      <c r="AN41" s="41"/>
     </row>
     <row r="42" spans="1:40" ht="15.75" customHeight="1">
       <c r="A42" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="44">
+      <c r="B42" s="41">
         <v>15</v>
       </c>
       <c r="C42" s="30" t="s">
@@ -4168,93 +4167,117 @@
       <c r="G42" s="9">
         <v>2</v>
       </c>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34">
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+      <c r="L42" s="32"/>
+      <c r="M42" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N42" s="35"/>
-      <c r="O42" s="35"/>
-      <c r="P42" s="35"/>
-      <c r="Q42" s="35"/>
-      <c r="R42" s="35"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="36">
+      <c r="N42" s="33"/>
+      <c r="O42" s="33"/>
+      <c r="P42" s="33"/>
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="34">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="U42" s="37"/>
-      <c r="V42" s="37"/>
-      <c r="W42" s="37"/>
-      <c r="X42" s="37"/>
-      <c r="Y42" s="37"/>
-      <c r="Z42" s="37"/>
-      <c r="AA42" s="37"/>
-      <c r="AB42" s="37"/>
-      <c r="AC42" s="37"/>
-      <c r="AD42" s="37"/>
-      <c r="AE42" s="38">
+      <c r="U42" s="35"/>
+      <c r="V42" s="35"/>
+      <c r="W42" s="35"/>
+      <c r="X42" s="35"/>
+      <c r="Y42" s="35"/>
+      <c r="Z42" s="35"/>
+      <c r="AA42" s="35"/>
+      <c r="AB42" s="35"/>
+      <c r="AC42" s="35"/>
+      <c r="AD42" s="35"/>
+      <c r="AE42" s="36">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
-      <c r="AF42" s="39"/>
-      <c r="AG42" s="40">
+      <c r="AF42" s="37"/>
+      <c r="AG42" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="AH42" s="41"/>
-      <c r="AI42" s="43"/>
-      <c r="AJ42" s="43"/>
-      <c r="AK42" s="43"/>
-      <c r="AL42" s="43"/>
+      <c r="AH42" s="39"/>
+      <c r="AI42" s="40"/>
+      <c r="AJ42" s="40"/>
+      <c r="AK42" s="40"/>
+      <c r="AL42" s="40"/>
       <c r="AM42" s="4"/>
-      <c r="AN42" s="44"/>
+      <c r="AN42" s="41"/>
     </row>
     <row r="43" spans="1:40" ht="15.75" customHeight="1">
-      <c r="A43" s="5"/>
-      <c r="B43" s="4"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="6"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="6"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="6"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="6"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="6"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="6"/>
-      <c r="AB43" s="6"/>
-      <c r="AC43" s="6"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="8"/>
-      <c r="AJ43" s="8"/>
-      <c r="AK43" s="8"/>
-      <c r="AL43" s="8"/>
+      <c r="A43" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="41">
+        <v>15</v>
+      </c>
+      <c r="C43" s="30" t="s">
+        <v>113</v>
+      </c>
+      <c r="D43" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="E43" s="30">
+        <v>1660289</v>
+      </c>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9">
+        <v>2</v>
+      </c>
+      <c r="H43" s="32"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
+      <c r="L43" s="32"/>
+      <c r="M43" s="32">
+        <f t="shared" ref="M43" si="13">SUM(H43:L43)</f>
+        <v>0</v>
+      </c>
+      <c r="N43" s="33"/>
+      <c r="O43" s="33"/>
+      <c r="P43" s="33"/>
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33"/>
+      <c r="S43" s="33"/>
+      <c r="T43" s="34">
+        <f t="shared" ref="T43" si="14">SUM(N43:S43)</f>
+        <v>0</v>
+      </c>
+      <c r="U43" s="35"/>
+      <c r="V43" s="35"/>
+      <c r="W43" s="35"/>
+      <c r="X43" s="35"/>
+      <c r="Y43" s="35"/>
+      <c r="Z43" s="35"/>
+      <c r="AA43" s="35"/>
+      <c r="AB43" s="35"/>
+      <c r="AC43" s="35"/>
+      <c r="AD43" s="35"/>
+      <c r="AE43" s="36">
+        <f t="shared" ref="AE43" si="15">SUM(U43:AD43)</f>
+        <v>0</v>
+      </c>
+      <c r="AF43" s="37"/>
+      <c r="AG43" s="38">
+        <f t="shared" ref="AG43" si="16">SUM(M43,T43,AE43)</f>
+        <v>0</v>
+      </c>
+      <c r="AH43" s="39"/>
+      <c r="AI43" s="40"/>
+      <c r="AJ43" s="40"/>
+      <c r="AK43" s="40"/>
+      <c r="AL43" s="40"/>
       <c r="AM43" s="4"/>
-      <c r="AN43" s="4"/>
+      <c r="AN43" s="41"/>
     </row>
     <row r="44" spans="1:40" ht="15.75" customHeight="1">
       <c r="A44" s="5"/>
@@ -4931,7 +4954,7 @@
     <row r="60" spans="1:40" ht="15.75" customHeight="1">
       <c r="A60" s="5"/>
       <c r="B60" s="4"/>
-      <c r="C60" s="86"/>
+      <c r="C60" s="81"/>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="5"/>
@@ -5226,15 +5249,15 @@
       <c r="A67" s="5"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
-      <c r="D67" s="87"/>
+      <c r="D67" s="82"/>
       <c r="E67" s="4"/>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="88"/>
-      <c r="I67" s="88"/>
-      <c r="J67" s="88"/>
-      <c r="K67" s="88"/>
-      <c r="L67" s="88"/>
+      <c r="H67" s="83"/>
+      <c r="I67" s="83"/>
+      <c r="J67" s="83"/>
+      <c r="K67" s="83"/>
+      <c r="L67" s="83"/>
       <c r="M67" s="5"/>
       <c r="N67" s="6"/>
       <c r="O67" s="6"/>
@@ -5268,15 +5291,15 @@
       <c r="A68" s="5"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
-      <c r="D68" s="87"/>
+      <c r="D68" s="82"/>
       <c r="E68" s="4"/>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="88"/>
-      <c r="I68" s="88"/>
-      <c r="J68" s="88"/>
-      <c r="K68" s="88"/>
-      <c r="L68" s="88"/>
+      <c r="H68" s="83"/>
+      <c r="I68" s="83"/>
+      <c r="J68" s="83"/>
+      <c r="K68" s="83"/>
+      <c r="L68" s="83"/>
       <c r="M68" s="5"/>
       <c r="N68" s="6"/>
       <c r="O68" s="6"/>
@@ -5310,15 +5333,15 @@
       <c r="A69" s="5"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
-      <c r="D69" s="87"/>
+      <c r="D69" s="82"/>
       <c r="E69" s="4"/>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="88"/>
-      <c r="I69" s="88"/>
-      <c r="J69" s="88"/>
-      <c r="K69" s="88"/>
-      <c r="L69" s="88"/>
+      <c r="H69" s="83"/>
+      <c r="I69" s="83"/>
+      <c r="J69" s="83"/>
+      <c r="K69" s="83"/>
+      <c r="L69" s="83"/>
       <c r="M69" s="5"/>
       <c r="N69" s="6"/>
       <c r="O69" s="6"/>
@@ -5356,11 +5379,11 @@
       <c r="E70" s="4"/>
       <c r="F70" s="5"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="88"/>
-      <c r="I70" s="88"/>
-      <c r="J70" s="88"/>
-      <c r="K70" s="88"/>
-      <c r="L70" s="88"/>
+      <c r="H70" s="83"/>
+      <c r="I70" s="83"/>
+      <c r="J70" s="83"/>
+      <c r="K70" s="83"/>
+      <c r="L70" s="83"/>
       <c r="M70" s="5"/>
       <c r="N70" s="6"/>
       <c r="O70" s="6"/>
@@ -5398,11 +5421,11 @@
       <c r="E71" s="4"/>
       <c r="F71" s="5"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="88"/>
-      <c r="I71" s="88"/>
-      <c r="J71" s="88"/>
-      <c r="K71" s="88"/>
-      <c r="L71" s="88"/>
+      <c r="H71" s="83"/>
+      <c r="I71" s="83"/>
+      <c r="J71" s="83"/>
+      <c r="K71" s="83"/>
+      <c r="L71" s="83"/>
       <c r="M71" s="5"/>
       <c r="N71" s="6"/>
       <c r="O71" s="6"/>
@@ -5440,11 +5463,11 @@
       <c r="E72" s="4"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="88"/>
-      <c r="I72" s="88"/>
-      <c r="J72" s="88"/>
-      <c r="K72" s="88"/>
-      <c r="L72" s="88"/>
+      <c r="H72" s="83"/>
+      <c r="I72" s="83"/>
+      <c r="J72" s="83"/>
+      <c r="K72" s="83"/>
+      <c r="L72" s="83"/>
       <c r="M72" s="5"/>
       <c r="N72" s="6"/>
       <c r="O72" s="6"/>
@@ -5482,11 +5505,11 @@
       <c r="E73" s="4"/>
       <c r="F73" s="5"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="88"/>
-      <c r="I73" s="88"/>
-      <c r="J73" s="88"/>
-      <c r="K73" s="88"/>
-      <c r="L73" s="88"/>
+      <c r="H73" s="83"/>
+      <c r="I73" s="83"/>
+      <c r="J73" s="83"/>
+      <c r="K73" s="83"/>
+      <c r="L73" s="83"/>
       <c r="M73" s="5"/>
       <c r="N73" s="6"/>
       <c r="O73" s="6"/>
@@ -5524,11 +5547,11 @@
       <c r="E74" s="4"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="88"/>
-      <c r="I74" s="88"/>
-      <c r="J74" s="88"/>
-      <c r="K74" s="88"/>
-      <c r="L74" s="88"/>
+      <c r="H74" s="83"/>
+      <c r="I74" s="83"/>
+      <c r="J74" s="83"/>
+      <c r="K74" s="83"/>
+      <c r="L74" s="83"/>
       <c r="M74" s="5"/>
       <c r="N74" s="6"/>
       <c r="O74" s="6"/>
@@ -5566,11 +5589,11 @@
       <c r="E75" s="4"/>
       <c r="F75" s="5"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="88"/>
-      <c r="I75" s="88"/>
-      <c r="J75" s="88"/>
-      <c r="K75" s="88"/>
-      <c r="L75" s="88"/>
+      <c r="H75" s="83"/>
+      <c r="I75" s="83"/>
+      <c r="J75" s="83"/>
+      <c r="K75" s="83"/>
+      <c r="L75" s="83"/>
       <c r="M75" s="5"/>
       <c r="N75" s="6"/>
       <c r="O75" s="6"/>
@@ -5608,11 +5631,11 @@
       <c r="E76" s="4"/>
       <c r="F76" s="5"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="88"/>
-      <c r="I76" s="88"/>
-      <c r="J76" s="88"/>
-      <c r="K76" s="88"/>
-      <c r="L76" s="88"/>
+      <c r="H76" s="83"/>
+      <c r="I76" s="83"/>
+      <c r="J76" s="83"/>
+      <c r="K76" s="83"/>
+      <c r="L76" s="83"/>
       <c r="M76" s="5"/>
       <c r="N76" s="6"/>
       <c r="O76" s="6"/>
@@ -5650,11 +5673,11 @@
       <c r="E77" s="4"/>
       <c r="F77" s="5"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="88"/>
-      <c r="I77" s="88"/>
-      <c r="J77" s="88"/>
-      <c r="K77" s="88"/>
-      <c r="L77" s="88"/>
+      <c r="H77" s="83"/>
+      <c r="I77" s="83"/>
+      <c r="J77" s="83"/>
+      <c r="K77" s="83"/>
+      <c r="L77" s="83"/>
       <c r="M77" s="5"/>
       <c r="N77" s="6"/>
       <c r="O77" s="6"/>
@@ -5688,15 +5711,15 @@
       <c r="A78" s="5"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
-      <c r="D78" s="87"/>
+      <c r="D78" s="82"/>
       <c r="E78" s="4"/>
       <c r="F78" s="5"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="88"/>
-      <c r="I78" s="88"/>
-      <c r="J78" s="88"/>
-      <c r="K78" s="88"/>
-      <c r="L78" s="88"/>
+      <c r="H78" s="83"/>
+      <c r="I78" s="83"/>
+      <c r="J78" s="83"/>
+      <c r="K78" s="83"/>
+      <c r="L78" s="83"/>
       <c r="M78" s="5"/>
       <c r="N78" s="6"/>
       <c r="O78" s="6"/>
@@ -5730,15 +5753,15 @@
       <c r="A79" s="5"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
-      <c r="D79" s="87"/>
+      <c r="D79" s="82"/>
       <c r="E79" s="4"/>
       <c r="F79" s="5"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="88"/>
-      <c r="I79" s="88"/>
-      <c r="J79" s="88"/>
-      <c r="K79" s="88"/>
-      <c r="L79" s="88"/>
+      <c r="H79" s="83"/>
+      <c r="I79" s="83"/>
+      <c r="J79" s="83"/>
+      <c r="K79" s="83"/>
+      <c r="L79" s="83"/>
       <c r="M79" s="5"/>
       <c r="N79" s="6"/>
       <c r="O79" s="6"/>
@@ -5771,16 +5794,16 @@
     <row r="80" spans="1:40" ht="15.75" customHeight="1">
       <c r="A80" s="5"/>
       <c r="B80" s="4"/>
-      <c r="C80" s="89"/>
-      <c r="D80" s="87"/>
+      <c r="C80" s="84"/>
+      <c r="D80" s="82"/>
       <c r="E80" s="4"/>
       <c r="F80" s="5"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="88"/>
-      <c r="I80" s="88"/>
-      <c r="J80" s="88"/>
-      <c r="K80" s="88"/>
-      <c r="L80" s="88"/>
+      <c r="H80" s="83"/>
+      <c r="I80" s="83"/>
+      <c r="J80" s="83"/>
+      <c r="K80" s="83"/>
+      <c r="L80" s="83"/>
       <c r="M80" s="5"/>
       <c r="N80" s="6"/>
       <c r="O80" s="6"/>
@@ -5813,16 +5836,16 @@
     <row r="81" spans="1:40" ht="15.75" customHeight="1">
       <c r="A81" s="5"/>
       <c r="B81" s="4"/>
-      <c r="C81" s="89"/>
-      <c r="D81" s="87"/>
+      <c r="C81" s="84"/>
+      <c r="D81" s="82"/>
       <c r="E81" s="4"/>
       <c r="F81" s="5"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="88"/>
-      <c r="I81" s="88"/>
-      <c r="J81" s="88"/>
-      <c r="K81" s="88"/>
-      <c r="L81" s="88"/>
+      <c r="H81" s="83"/>
+      <c r="I81" s="83"/>
+      <c r="J81" s="83"/>
+      <c r="K81" s="83"/>
+      <c r="L81" s="83"/>
       <c r="M81" s="5"/>
       <c r="N81" s="6"/>
       <c r="O81" s="6"/>
@@ -5855,16 +5878,16 @@
     <row r="82" spans="1:40" ht="15.75" customHeight="1">
       <c r="A82" s="5"/>
       <c r="B82" s="4"/>
-      <c r="C82" s="89"/>
-      <c r="D82" s="87"/>
+      <c r="C82" s="84"/>
+      <c r="D82" s="82"/>
       <c r="E82" s="4"/>
       <c r="F82" s="5"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="88"/>
-      <c r="I82" s="88"/>
-      <c r="J82" s="88"/>
-      <c r="K82" s="88"/>
-      <c r="L82" s="88"/>
+      <c r="H82" s="83"/>
+      <c r="I82" s="83"/>
+      <c r="J82" s="83"/>
+      <c r="K82" s="83"/>
+      <c r="L82" s="83"/>
       <c r="M82" s="5"/>
       <c r="N82" s="6"/>
       <c r="O82" s="6"/>
@@ -5897,7 +5920,7 @@
     <row r="83" spans="1:40" ht="15.75" customHeight="1">
       <c r="A83" s="5"/>
       <c r="B83" s="4"/>
-      <c r="C83" s="89"/>
+      <c r="C83" s="84"/>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
       <c r="F83" s="5"/>
@@ -5939,7 +5962,7 @@
     <row r="84" spans="1:40" ht="15.75" customHeight="1">
       <c r="A84" s="5"/>
       <c r="B84" s="4"/>
-      <c r="C84" s="89"/>
+      <c r="C84" s="84"/>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
       <c r="F84" s="5"/>
@@ -5981,7 +6004,7 @@
     <row r="85" spans="1:40" ht="15.75" customHeight="1">
       <c r="A85" s="5"/>
       <c r="B85" s="4"/>
-      <c r="C85" s="89"/>
+      <c r="C85" s="84"/>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
       <c r="F85" s="5"/>
@@ -6023,7 +6046,7 @@
     <row r="86" spans="1:40" ht="15.75" customHeight="1">
       <c r="A86" s="5"/>
       <c r="B86" s="4"/>
-      <c r="C86" s="89"/>
+      <c r="C86" s="84"/>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
       <c r="F86" s="5"/>
@@ -6065,7 +6088,7 @@
     <row r="87" spans="1:40" ht="15.75" customHeight="1">
       <c r="A87" s="5"/>
       <c r="B87" s="4"/>
-      <c r="C87" s="89"/>
+      <c r="C87" s="84"/>
       <c r="D87" s="4"/>
       <c r="E87" s="4"/>
       <c r="F87" s="5"/>
@@ -6107,7 +6130,7 @@
     <row r="88" spans="1:40" ht="15.75" customHeight="1">
       <c r="A88" s="5"/>
       <c r="B88" s="4"/>
-      <c r="C88" s="89"/>
+      <c r="C88" s="84"/>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
       <c r="F88" s="5"/>
@@ -6149,7 +6172,7 @@
     <row r="89" spans="1:40" ht="15.75" customHeight="1">
       <c r="A89" s="5"/>
       <c r="B89" s="4"/>
-      <c r="C89" s="89"/>
+      <c r="C89" s="84"/>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
       <c r="F89" s="5"/>
@@ -6191,7 +6214,7 @@
     <row r="90" spans="1:40" ht="15.75" customHeight="1">
       <c r="A90" s="5"/>
       <c r="B90" s="4"/>
-      <c r="C90" s="89"/>
+      <c r="C90" s="84"/>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
       <c r="F90" s="5"/>
@@ -6233,7 +6256,7 @@
     <row r="91" spans="1:40" ht="15.75" customHeight="1">
       <c r="A91" s="5"/>
       <c r="B91" s="4"/>
-      <c r="C91" s="89"/>
+      <c r="C91" s="84"/>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
       <c r="F91" s="5"/>
@@ -6275,7 +6298,7 @@
     <row r="92" spans="1:40" ht="15.75" customHeight="1">
       <c r="A92" s="5"/>
       <c r="B92" s="4"/>
-      <c r="C92" s="89"/>
+      <c r="C92" s="84"/>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
       <c r="F92" s="5"/>
@@ -6485,7 +6508,7 @@
     <row r="97" spans="1:40" ht="15.75" customHeight="1">
       <c r="A97" s="5"/>
       <c r="B97" s="4"/>
-      <c r="C97" s="89"/>
+      <c r="C97" s="84"/>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
       <c r="F97" s="5"/>
@@ -44463,7 +44486,7 @@
     <mergeCell ref="N3:S3"/>
     <mergeCell ref="U3:AD3"/>
   </mergeCells>
-  <conditionalFormatting sqref="M5:M42">
+  <conditionalFormatting sqref="M5:M43">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThanOrEqual">
       <formula>"M4"</formula>
     </cfRule>
